--- a/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77117</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67867</t>
+          <t>67483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146438</t>
+          <t>147133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151603</t>
+          <t>151608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62332</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67853</t>
+          <t>67882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62235</t>
+          <t>62242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66856</t>
+          <t>66849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127019</t>
+          <t>126408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133855</t>
+          <t>133771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77569</t>
+          <t>77977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135845</t>
+          <t>136247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141509</t>
+          <t>141517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142445</t>
+          <t>142061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149339</t>
+          <t>149377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142860</t>
+          <t>141978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>147898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287566</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296447</t>
+          <t>296077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>65948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74923</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82604</t>
+          <t>82618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143470</t>
+          <t>143862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151105</t>
+          <t>151534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>68571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74258</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66703</t>
+          <t>67083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71748</t>
+          <t>71750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138872</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145310</t>
+          <t>145353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>485841</t>
+          <t>485676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>495772</t>
+          <t>496336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>507201</t>
+          <t>507912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>519564</t>
+          <t>519367</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>996905</t>
+          <t>996995</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1013109</t>
+          <t>1012675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>55384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>60547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128035</t>
+          <t>127357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133912</t>
+          <t>133876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>64490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128693</t>
+          <t>128227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133276</t>
+          <t>133282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65766</t>
+          <t>65761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>64323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133112</t>
+          <t>133129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129328</t>
+          <t>129935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135565</t>
+          <t>135814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156550</t>
+          <t>156742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289134</t>
+          <t>288659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296076</t>
+          <t>296269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85607</t>
+          <t>85943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92150</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86526</t>
+          <t>86524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91380</t>
+          <t>91388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175121</t>
+          <t>175485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182877</t>
+          <t>183144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48482</t>
+          <t>48435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68848</t>
+          <t>69101</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>73612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120502</t>
+          <t>120554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>126743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29724</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>455118</t>
+          <t>454921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>467943</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>524314</t>
+          <t>524000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>533482</t>
+          <t>533433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>984551</t>
+          <t>984557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>999805</t>
+          <t>999130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>58857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64195</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68598</t>
+          <t>68783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76316</t>
+          <t>76395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130174</t>
+          <t>130501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139519</t>
+          <t>139596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73959</t>
+          <t>74212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81130</t>
+          <t>81157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163804</t>
+          <t>164083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172590</t>
+          <t>172809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44308</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57014</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103305</t>
+          <t>103120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153608</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162293</t>
+          <t>162075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157308</t>
+          <t>157054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>166104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314636</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326812</t>
+          <t>326785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88886</t>
+          <t>89080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>97658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87360</t>
+          <t>87192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96122</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180544</t>
+          <t>180749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192345</t>
+          <t>192137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58858</t>
+          <t>58878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59481</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65889</t>
+          <t>66418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113953</t>
+          <t>114642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123631</t>
+          <t>123939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>35295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>37205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>43441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67895</t>
+          <t>66799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>489055</t>
+          <t>488781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>505293</t>
+          <t>505128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>533795</t>
+          <t>532987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>550435</t>
+          <t>550249</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1026373</t>
+          <t>1027469</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1051475</t>
+          <t>1050827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96428</t>
+          <t>96097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102733</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129436</t>
+          <t>129775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136422</t>
+          <t>136404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229437</t>
+          <t>228936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238455</t>
+          <t>237958</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86263</t>
+          <t>86524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93456</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85564</t>
+          <t>86220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93512</t>
+          <t>93668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175784</t>
+          <t>175287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>185714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42649</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>49664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54647</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>62591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101009</t>
+          <t>101380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>111216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25999</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206299</t>
+          <t>206731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215762</t>
+          <t>215309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199743</t>
+          <t>199794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211443</t>
+          <t>211867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411098</t>
+          <t>410776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425570</t>
+          <t>424919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105079</t>
+          <t>104650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114545</t>
+          <t>114380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142924</t>
+          <t>142308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155100</t>
+          <t>154895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251207</t>
+          <t>250727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267054</t>
+          <t>267106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57177</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>68697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>121392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133362</t>
+          <t>133762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>44345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31508</t>
+          <t>31876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93003</t>
+          <t>93879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>612713</t>
+          <t>613808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>632073</t>
+          <t>632665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>693809</t>
+          <t>695227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>717717</t>
+          <t>717349</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314375</t>
+          <t>1313499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344897</t>
+          <t>1344501</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
